--- a/CONSENT.xlsx
+++ b/CONSENT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4987431A-1AB3-4A50-8CAD-74143813515A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421B0CE4-0838-4FE2-BAD7-6B67EE28195C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
   <si>
     <t xml:space="preserve">REG NUM </t>
   </si>
@@ -214,6 +214,12 @@
   </si>
   <si>
     <t>JK04K3984</t>
+  </si>
+  <si>
+    <t>JK13K1948</t>
+  </si>
+  <si>
+    <t>Muzamil RM</t>
   </si>
 </sst>
 </file>
@@ -286,6 +292,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -295,28 +304,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -333,18 +339,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -395,20 +402,20 @@
   <autoFilter ref="A2:C25" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="REG NUM " dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="CONSENT " dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="DATE" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="CONSENT " dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="DATE" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="F2:H13" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="F2:H13" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="F2:H13" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Name" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Reg Num" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Date" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Name" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Reg Num" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Date" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -677,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -690,18 +697,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -917,7 +924,7 @@
       <c r="G11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="5">
         <v>45960</v>
       </c>
     </row>
@@ -939,7 +946,7 @@
       <c r="G12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="5">
         <v>45960</v>
       </c>
     </row>
@@ -961,7 +968,7 @@
       <c r="G13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="5">
         <v>45960</v>
       </c>
     </row>
@@ -1078,7 +1085,7 @@
       <c r="H20" s="1"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1094,7 +1101,7 @@
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
+      <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="3"/>
       <c r="D22" s="1"/>
@@ -1114,9 +1121,15 @@
       <c r="H23" s="1"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="3"/>
+      <c r="A24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="3">
+        <v>45960</v>
+      </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -1124,7 +1137,7 @@
       <c r="H24" s="1"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
+      <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="3"/>
       <c r="D25" s="1"/>
@@ -1132,6 +1145,11 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/CONSENT.xlsx
+++ b/CONSENT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421B0CE4-0838-4FE2-BAD7-6B67EE28195C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D34E241-BEB1-4E56-8FAE-953D3AE6DDCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
   <si>
     <t xml:space="preserve">REG NUM </t>
   </si>
@@ -220,13 +220,16 @@
   </si>
   <si>
     <t>Muzamil RM</t>
+  </si>
+  <si>
+    <t>JK13K1687</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,6 +260,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -278,7 +288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -304,11 +314,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -337,21 +363,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -402,20 +413,20 @@
   <autoFilter ref="A2:C25" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="REG NUM " dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="CONSENT " dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="DATE" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="CONSENT " dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="DATE" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="F2:H13" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="F2:H13" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="F2:H13" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Name" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Reg Num" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Date" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Name" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Reg Num" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Date" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1101,9 +1112,15 @@
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="3"/>
+      <c r="A22" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="3">
+        <v>45960</v>
+      </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>

--- a/CONSENT.xlsx
+++ b/CONSENT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D34E241-BEB1-4E56-8FAE-953D3AE6DDCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6BCDA3-D678-42CB-9FF0-76E947F70FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="67">
   <si>
     <t xml:space="preserve">REG NUM </t>
   </si>
@@ -223,6 +223,9 @@
   </si>
   <si>
     <t>JK13K1687</t>
+  </si>
+  <si>
+    <t>HJUUJ</t>
   </si>
 </sst>
 </file>
@@ -305,6 +308,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -314,7 +318,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -708,18 +711,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1112,7 +1115,7 @@
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="6" t="s">
         <v>65</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1154,8 +1157,12 @@
       <c r="H24" s="1"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
+      <c r="A25" s="2">
+        <v>123</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="C25" s="3"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>

--- a/CONSENT.xlsx
+++ b/CONSENT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6BCDA3-D678-42CB-9FF0-76E947F70FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE62D1C-B6C0-4D2B-AC53-C9D76DB40FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
   <si>
     <t xml:space="preserve">REG NUM </t>
   </si>
@@ -223,9 +223,6 @@
   </si>
   <si>
     <t>JK13K1687</t>
-  </si>
-  <si>
-    <t>HJUUJ</t>
   </si>
 </sst>
 </file>
@@ -1157,12 +1154,8 @@
       <c r="H24" s="1"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>123</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
       <c r="C25" s="3"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>

--- a/CONSENT.xlsx
+++ b/CONSENT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE62D1C-B6C0-4D2B-AC53-C9D76DB40FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEC7CC1-55D2-4D25-A520-703922395ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1154,8 +1154,12 @@
       <c r="H24" s="1"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
+      <c r="A25" s="2">
+        <v>123555</v>
+      </c>
+      <c r="B25" s="2">
+        <v>45635434</v>
+      </c>
       <c r="C25" s="3"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>

--- a/CONSENT.xlsx
+++ b/CONSENT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6BCDA3-D678-42CB-9FF0-76E947F70FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA440C5-4FD4-4D49-A599-F93106BE828A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
   <si>
     <t xml:space="preserve">REG NUM </t>
   </si>
@@ -223,9 +223,6 @@
   </si>
   <si>
     <t>JK13K1687</t>
-  </si>
-  <si>
-    <t>HJUUJ</t>
   </si>
 </sst>
 </file>
@@ -1157,12 +1154,8 @@
       <c r="H24" s="1"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>123</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
       <c r="C25" s="3"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>

--- a/CONSENT.xlsx
+++ b/CONSENT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEC7CC1-55D2-4D25-A520-703922395ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB0F0E9-CCA4-4DD6-8076-29316B89630E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -229,7 +229,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,13 +260,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -288,7 +281,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -305,7 +298,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -409,8 +401,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A2:C25" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A2:C25" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A2:C23" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A2:C23" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="REG NUM " dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="CONSENT " dataDxfId="6"/>
@@ -695,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -708,18 +700,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1112,11 +1104,11 @@
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>65</v>
+      <c r="A22" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="C22" s="3">
         <v>45960</v>
@@ -1127,10 +1119,16 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="3"/>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="5">
+        <v>45960</v>
+      </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -1138,39 +1136,21 @@
       <c r="H23" s="1"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="3">
-        <v>45960</v>
-      </c>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>123555</v>
-      </c>
-      <c r="B25" s="2">
-        <v>45635434</v>
-      </c>
-      <c r="C25" s="3"/>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/CONSENT.xlsx
+++ b/CONSENT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB0F0E9-CCA4-4DD6-8076-29316B89630E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C570B1-6CDB-488F-82FC-CEDCBFAA8479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="18000" windowHeight="9270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="68">
   <si>
     <t xml:space="preserve">REG NUM </t>
   </si>
@@ -223,6 +223,12 @@
   </si>
   <si>
     <t>JK13K1687</t>
+  </si>
+  <si>
+    <t>MUZAMIL ASHRAF</t>
+  </si>
+  <si>
+    <t>JK03Q9991</t>
   </si>
 </sst>
 </file>
@@ -413,8 +419,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="F2:H13" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="F2:H13" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="F2:H14" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="F2:H14" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Name" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Reg Num" dataDxfId="1"/>
@@ -987,9 +993,15 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" s="5">
+        <v>45961</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">

--- a/CONSENT.xlsx
+++ b/CONSENT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C570B1-6CDB-488F-82FC-CEDCBFAA8479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB927BAD-C587-4CEB-829F-B50989C3B7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="18000" windowHeight="9270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2550" yWindow="1005" windowWidth="20040" windowHeight="11715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="70">
   <si>
     <t xml:space="preserve">REG NUM </t>
   </si>
@@ -229,13 +229,19 @@
   </si>
   <si>
     <t>JK03Q9991</t>
+  </si>
+  <si>
+    <t>JK01BC2301</t>
+  </si>
+  <si>
+    <t>Customer/ nadeem farooq / 7006401858</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,6 +272,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -287,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -303,6 +315,12 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -407,8 +425,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A2:C23" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A2:C23" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A2:C24" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A2:C24" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="REG NUM " dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="CONSENT " dataDxfId="6"/>
@@ -697,7 +715,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="33" customWidth="1"/>
+    <col min="2" max="2" width="39.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.140625" customWidth="1"/>
     <col min="6" max="6" width="25.42578125" customWidth="1"/>
     <col min="7" max="7" width="18.5703125" customWidth="1"/>
@@ -706,18 +724,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1148,9 +1166,15 @@
       <c r="H23" s="1"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
+      <c r="A24" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="7">
+        <v>45965</v>
+      </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>

--- a/CONSENT.xlsx
+++ b/CONSENT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB927BAD-C587-4CEB-829F-B50989C3B7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C43AF75-D8AB-4A36-AB5C-7255063B8AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="1005" windowWidth="20040" windowHeight="11715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
